--- a/output.xlsx
+++ b/output.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="167" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,11 +57,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00CC0000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
@@ -88,7 +83,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00CC0000"/>
+      <color rgb="00207020"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -113,6 +108,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
         <bgColor rgb="00D9EAD3"/>
       </patternFill>
@@ -121,12 +122,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F3F3F3"/>
         <bgColor rgb="00F3F3F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -206,16 +201,13 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,76 +216,79 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -661,92 +656,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Portfolio Summary</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Generated: 2026-06-09 21:06:35</t>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Generated: 2026-06-11 11:43:19</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Total Cost Basis ($)</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>April Snapshot ($)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>April Snapshot Value</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="18" t="n">
         <v>5712900.84</v>
       </c>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="18" t="n">
+        <v>5712900.84</v>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Current Market Value</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>5706930.882719999</v>
+      <c r="B6" s="18" t="n">
+        <v>5979586.3030085</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>3949239.310000001</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>5818449.879999999</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Total Gain / Loss ($)</t>
         </is>
       </c>
       <c r="B7" s="20" t="n">
-        <v>-5969.957280000672</v>
-      </c>
+        <v>266685.4630085006</v>
+      </c>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Total Gain / Loss (%)</t>
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>-0.1044995781862839</v>
-      </c>
+        <v>4.668126937216377</v>
+      </c>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="19" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Ticker Type</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Market Value ($)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>% of Portfolio</t>
         </is>
@@ -759,10 +779,10 @@
         </is>
       </c>
       <c r="B11" s="23" t="n">
-        <v>271093.2287800001</v>
+        <v>266284.40597</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>4.750245523401072</v>
+        <v>4.453224562308344</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -772,10 +792,10 @@
         </is>
       </c>
       <c r="B12" s="26" t="n">
-        <v>919430.3216999999</v>
+        <v>1248510.0912685</v>
       </c>
       <c r="C12" s="27" t="n">
-        <v>16.11076672549058</v>
+        <v>20.87953962033024</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -785,10 +805,10 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>3218101.74224</v>
+        <v>3166486.21577</v>
       </c>
       <c r="C13" s="30" t="n">
-        <v>56.38935898074535</v>
+        <v>52.95493793904858</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -801,7 +821,7 @@
         <v>1281712.88</v>
       </c>
       <c r="C14" s="33" t="n">
-        <v>22.45888212665927</v>
+        <v>21.43480861468851</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -814,17 +834,17 @@
         <v>16592.71</v>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0.2907466437037292</v>
+        <v>0.2774892636243369</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
       <c r="B16" s="37" t="n">
-        <v>5706930.882719999</v>
+        <v>5979586.3030085</v>
       </c>
       <c r="C16" s="38" t="n">
         <v>100</v>
@@ -970,14 +990,14 @@
         <v>1</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>683.16</v>
+        <v>672.1</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -985,11 +1005,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N2" s="4" t="n">
-        <v>318212.51</v>
-      </c>
-      <c r="O2" s="8" t="n">
-        <v>211484.78</v>
+      <c r="N2" s="4">
+        <f>J2*E2</f>
+        <v/>
+      </c>
+      <c r="O2" s="8">
+        <f>N2-G2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1027,14 +1049,14 @@
         <v>1.03</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>177.1</v>
+        <v>174.25</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>100</v>
+        <v>1.58</v>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -1042,11 +1064,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N3" s="4" t="n">
-        <v>298349.21</v>
-      </c>
-      <c r="O3" s="8" t="n">
-        <v>187075.77</v>
+      <c r="N3" s="4">
+        <f>J3*E3</f>
+        <v/>
+      </c>
+      <c r="O3" s="8">
+        <f>N3-G3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -1066,10 +1090,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>805.58</v>
+        <v>100.7</v>
       </c>
       <c r="E4" t="n">
-        <v>338.913</v>
+        <v>2711.304</v>
       </c>
       <c r="F4" t="n">
         <v>176274.14</v>
@@ -1084,26 +1108,26 @@
         <v>1.42</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>114.99</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>32</v>
-      </c>
+        <v>113.65</v>
+      </c>
+      <c r="K4" s="9" t="n"/>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N4" s="4" t="n">
-        <v>38971.61</v>
-      </c>
-      <c r="O4" s="10" t="n">
-        <v>-57775.46</v>
+      <c r="N4" s="4">
+        <f>J4*E4</f>
+        <v/>
+      </c>
+      <c r="O4" s="8">
+        <f>N4-G4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1141,14 +1165,14 @@
         <v>2.09</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>207.26</v>
+        <v>199.47</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -1156,11 +1180,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N5" s="4" t="n">
-        <v>331674.45</v>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v>247820.51</v>
+      <c r="N5" s="4">
+        <f>J5*E5</f>
+        <v/>
+      </c>
+      <c r="O5" s="8">
+        <f>N5-G5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1198,14 +1224,14 @@
         <v>1.24</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>263.7</v>
+        <v>258.33</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>36</v>
+        <v>0.58</v>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -1213,11 +1239,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N6" s="4" t="n">
-        <v>265963.86</v>
-      </c>
-      <c r="O6" s="8" t="n">
-        <v>154820.49</v>
+      <c r="N6" s="4">
+        <f>J6*E6</f>
+        <v/>
+      </c>
+      <c r="O6" s="8">
+        <f>N6-G6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1255,14 +1283,14 @@
         <v>0.99</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>390.57</v>
+        <v>384.43</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1.36</v>
+        <v>0.77</v>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -1270,11 +1298,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N7" s="4" t="n">
-        <v>122779.59</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>65516.76</v>
+      <c r="N7" s="4">
+        <f>J7*E7</f>
+        <v/>
+      </c>
+      <c r="O7" s="8">
+        <f>N7-G7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1312,26 +1342,28 @@
         <v>0.62</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>287.39</v>
+        <v>286.55</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1.68</v>
+        <v>1</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N8" s="4" t="n">
-        <v>105753.77</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>53363.28</v>
+      <c r="N8" s="4">
+        <f>J8*E8</f>
+        <v/>
+      </c>
+      <c r="O8" s="8">
+        <f>N8-G8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1376,7 +1408,7 @@
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1384,11 +1416,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N9" s="4" t="n">
-        <v>100000.6</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>0</v>
+      <c r="N9" s="4">
+        <f>H9</f>
+        <v/>
+      </c>
+      <c r="O9" s="8">
+        <f>N9-G9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1408,10 +1442,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>415.92</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>187.499</v>
+        <v>937.495</v>
       </c>
       <c r="F10" t="n">
         <v>17544.33</v>
@@ -1426,26 +1460,28 @@
         <v>1.23</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>86.88</v>
+        <v>85.33</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N10" s="4" t="n">
-        <v>16289.91</v>
-      </c>
-      <c r="O10" s="10" t="n">
-        <v>-44150.47</v>
+      <c r="N10" s="4">
+        <f>J10*E10</f>
+        <v/>
+      </c>
+      <c r="O10" s="8">
+        <f>N10-G10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1483,26 +1519,28 @@
         <v>0.7</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>158.84</v>
+        <v>158.15</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>2.21</v>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N11" s="4" t="n">
-        <v>66859.41</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>5050.95</v>
+      <c r="N11" s="4">
+        <f>J11*E11</f>
+        <v/>
+      </c>
+      <c r="O11" s="8">
+        <f>N11-G11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1540,26 +1578,28 @@
         <v>0.59</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>32.39</v>
+        <v>32.495</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N12" s="4" t="n">
-        <v>52633.75</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>2665.15</v>
+      <c r="N12" s="4">
+        <f>J12*E12</f>
+        <v/>
+      </c>
+      <c r="O12" s="8">
+        <f>N12-G12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1597,24 +1637,28 @@
         <v>1.798</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>396.68</v>
-      </c>
-      <c r="K13" s="12" t="n"/>
+        <v>386.08</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M13" s="13" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="N13" s="4" t="n">
-        <v>41651.4</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>31599.99</v>
+      <c r="N13" s="4">
+        <f>J13*E13</f>
+        <v/>
+      </c>
+      <c r="O13" s="8">
+        <f>N13-G13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1652,26 +1696,28 @@
         <v>1.086</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>290.55</v>
+        <v>293.045</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>36</v>
+        <v>0.36</v>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M14" s="13" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M14" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="N14" s="4" t="n">
-        <v>34718.4</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>25991.54</v>
+      <c r="N14" s="4">
+        <f>J14*E14</f>
+        <v/>
+      </c>
+      <c r="O14" s="8">
+        <f>N14-G14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1709,26 +1755,28 @@
         <v>1.25</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>388.5</v>
+        <v>383.93</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N15" s="4" t="n">
-        <v>26732.3</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>436.66</v>
+      <c r="N15" s="4">
+        <f>J15*E15</f>
+        <v/>
+      </c>
+      <c r="O15" s="8">
+        <f>N15-G15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1766,26 +1814,28 @@
         <v>1</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>677.7</v>
+        <v>670.1</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1.03</v>
+        <v>0.82</v>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M16" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N16" s="4" t="n">
-        <v>13721.39</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>3190.94</v>
+      <c r="N16" s="4">
+        <f>J16*E16</f>
+        <v/>
+      </c>
+      <c r="O16" s="8">
+        <f>N16-G16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1823,14 +1873,14 @@
         <v>1</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>683.16</v>
+        <v>672.1</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -1838,11 +1888,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N17" s="4" t="n">
-        <v>313367.54</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>125850.07</v>
+      <c r="N17" s="4">
+        <f>J17*E17</f>
+        <v/>
+      </c>
+      <c r="O17" s="8">
+        <f>N17-G17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1880,26 +1932,28 @@
         <v>1</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>677.7</v>
+        <v>670.1</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>1.03</v>
+        <v>0.82</v>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M18" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N18" s="4" t="n">
-        <v>161310.22</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>12403.68</v>
+      <c r="N18" s="4">
+        <f>J18*E18</f>
+        <v/>
+      </c>
+      <c r="O18" s="8">
+        <f>N18-G18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1937,14 +1991,14 @@
         <v>1.03</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>177.1</v>
+        <v>174.25</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>100</v>
+        <v>1.58</v>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -1952,11 +2006,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N19" s="4" t="n">
-        <v>155285.35</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>58219.41</v>
+      <c r="N19" s="4">
+        <f>J19*E19</f>
+        <v/>
+      </c>
+      <c r="O19" s="8">
+        <f>N19-G19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1994,26 +2050,28 @@
         <v>0.92</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>83.81999999999999</v>
+        <v>83.60850000000001</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>2.66</v>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M20" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N20" s="4" t="n">
-        <v>79246.28</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>6110.57</v>
+      <c r="N20" s="4">
+        <f>J20*E20</f>
+        <v/>
+      </c>
+      <c r="O20" s="8">
+        <f>N20-G20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -2051,26 +2109,28 @@
         <v>0.98</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>154.3</v>
+        <v>153.14</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M21" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N21" s="4" t="n">
-        <v>72526.09</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>4137.28</v>
+      <c r="N21" s="4">
+        <f>J21*E21</f>
+        <v/>
+      </c>
+      <c r="O21" s="8">
+        <f>N21-G21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -2108,14 +2168,14 @@
         <v>1.24</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>263.7</v>
+        <v>258.33</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>36</v>
+        <v>0.58</v>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -2123,11 +2183,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N22" s="4" t="n">
-        <v>63970.98</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>26429.74</v>
+      <c r="N22" s="4">
+        <f>J22*E22</f>
+        <v/>
+      </c>
+      <c r="O22" s="8">
+        <f>N22-G22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -2172,7 +2234,7 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
@@ -2180,11 +2242,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N23" s="4" t="n">
-        <v>50054.78</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>0</v>
+      <c r="N23" s="4">
+        <f>H23</f>
+        <v/>
+      </c>
+      <c r="O23" s="8">
+        <f>N23-G23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -2222,26 +2286,28 @@
         <v>0.7</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>158.84</v>
+        <v>158.15</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>2.21</v>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N24" s="4" t="n">
-        <v>47044.28</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>2044.29</v>
+      <c r="N24" s="4">
+        <f>J24*E24</f>
+        <v/>
+      </c>
+      <c r="O24" s="8">
+        <f>N24-G24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -2279,26 +2345,28 @@
         <v>0.59</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>32.39</v>
+        <v>32.495</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N25" s="4" t="n">
-        <v>47840.03</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>2568.04</v>
+      <c r="N25" s="4">
+        <f>J25*E25</f>
+        <v/>
+      </c>
+      <c r="O25" s="8">
+        <f>N25-G25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -2336,14 +2404,14 @@
         <v>1.05</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>56.49</v>
+        <v>55.51</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>60</v>
+        <v>0.6</v>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -2351,11 +2419,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N26" s="4" t="n">
-        <v>31820.76</v>
-      </c>
-      <c r="O26" s="8" t="n">
-        <v>6741.63</v>
+      <c r="N26" s="4">
+        <f>J26*E26</f>
+        <v/>
+      </c>
+      <c r="O26" s="8">
+        <f>N26-G26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -2400,7 +2470,7 @@
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -2408,11 +2478,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N27" s="4" t="n">
-        <v>350112.5</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>128429.86</v>
+      <c r="N27" s="4">
+        <f>H27</f>
+        <v/>
+      </c>
+      <c r="O27" s="8">
+        <f>N27-G27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -2457,7 +2529,7 @@
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
@@ -2465,11 +2537,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N28" s="4" t="n">
-        <v>213631.55</v>
-      </c>
-      <c r="O28" s="8" t="n">
-        <v>0</v>
+      <c r="N28" s="4">
+        <f>H28</f>
+        <v/>
+      </c>
+      <c r="O28" s="8">
+        <f>N28-G28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -2514,7 +2588,7 @@
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -2522,11 +2596,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N29" s="4" t="n">
-        <v>205776.07</v>
-      </c>
-      <c r="O29" s="8" t="n">
-        <v>50081.97</v>
+      <c r="N29" s="4">
+        <f>H29</f>
+        <v/>
+      </c>
+      <c r="O29" s="8">
+        <f>N29-G29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -2571,7 +2647,7 @@
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -2579,11 +2655,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N30" s="4" t="n">
-        <v>1477.69</v>
-      </c>
-      <c r="O30" s="8" t="n">
-        <v>59.24</v>
+      <c r="N30" s="4">
+        <f>H30</f>
+        <v/>
+      </c>
+      <c r="O30" s="8">
+        <f>N30-G30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -2621,14 +2699,14 @@
         <v>1</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>257.15</v>
+        <v>252.98</v>
       </c>
       <c r="K31" s="5" t="n">
         <v>1.03</v>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -2636,11 +2714,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N31" s="4" t="n">
-        <v>135469.19</v>
-      </c>
-      <c r="O31" s="8" t="n">
-        <v>50982.2</v>
+      <c r="N31" s="4">
+        <f>J31*E31</f>
+        <v/>
+      </c>
+      <c r="O31" s="8">
+        <f>N31-G31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -2678,26 +2758,28 @@
         <v>0.92</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>83.81999999999999</v>
+        <v>83.60850000000001</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>2.66</v>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M32" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N32" s="4" t="n">
-        <v>78610.34</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>6363.95</v>
+      <c r="N32" s="4">
+        <f>J32*E32</f>
+        <v/>
+      </c>
+      <c r="O32" s="8">
+        <f>N32-G32</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -2735,24 +2817,28 @@
         <v>1.798</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>396.68</v>
-      </c>
-      <c r="K33" s="12" t="n"/>
+        <v>386.08</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M33" s="13" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M33" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="N33" s="4" t="n">
-        <v>75369.2</v>
-      </c>
-      <c r="O33" s="8" t="n">
-        <v>31385.4</v>
+      <c r="N33" s="4">
+        <f>J33*E33</f>
+        <v/>
+      </c>
+      <c r="O33" s="8">
+        <f>N33-G33</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -2790,26 +2876,28 @@
         <v>2.202</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>208.19</v>
+        <v>201.43</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>48</v>
+        <v>0.02</v>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M34" s="13" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M34" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="N34" s="4" t="n">
-        <v>52855.07</v>
-      </c>
-      <c r="O34" s="8" t="n">
-        <v>34447.67</v>
+      <c r="N34" s="4">
+        <f>J34*E34</f>
+        <v/>
+      </c>
+      <c r="O34" s="8">
+        <f>N34-G34</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -2847,26 +2935,28 @@
         <v>0.59</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>32.39</v>
+        <v>32.495</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M35" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N35" s="4" t="n">
-        <v>54476.19</v>
-      </c>
-      <c r="O35" s="8" t="n">
-        <v>2833.75</v>
+      <c r="N35" s="4">
+        <f>J35*E35</f>
+        <v/>
+      </c>
+      <c r="O35" s="8">
+        <f>N35-G35</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -2904,14 +2994,14 @@
         <v>2.12</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>67.37</v>
+        <v>64.86</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -2919,11 +3009,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N36" s="4" t="n">
-        <v>42929.38</v>
-      </c>
-      <c r="O36" s="8" t="n">
-        <v>23259.1</v>
+      <c r="N36" s="4">
+        <f>J36*E36</f>
+        <v/>
+      </c>
+      <c r="O36" s="8">
+        <f>N36-G36</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -2961,26 +3053,28 @@
         <v>1.086</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>290.55</v>
+        <v>293.045</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>36</v>
+        <v>0.36</v>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M37" s="13" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M37" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="N37" s="4" t="n">
-        <v>29324.05</v>
-      </c>
-      <c r="O37" s="8" t="n">
-        <v>12603.96</v>
+      <c r="N37" s="4">
+        <f>J37*E37</f>
+        <v/>
+      </c>
+      <c r="O37" s="8">
+        <f>N37-G37</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -3018,26 +3112,28 @@
         <v>1.97</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>591.01</v>
+        <v>589.5599999999999</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M38" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N38" s="4" t="n">
-        <v>21552.36</v>
-      </c>
-      <c r="O38" s="8" t="n">
-        <v>11634.69</v>
+      <c r="N38" s="4">
+        <f>J38*E38</f>
+        <v/>
+      </c>
+      <c r="O38" s="8">
+        <f>N38-G38</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -3075,26 +3171,28 @@
         <v>1.64</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>154.75</v>
+        <v>154.65</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>73</v>
+        <v>0.73</v>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M39" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N39" s="4" t="n">
-        <v>18905.81</v>
-      </c>
-      <c r="O39" s="8" t="n">
-        <v>8230.299999999999</v>
+      <c r="N39" s="4">
+        <f>J39*E39</f>
+        <v/>
+      </c>
+      <c r="O39" s="8">
+        <f>N39-G39</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -3132,26 +3230,28 @@
         <v>1.41</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>274.63</v>
+        <v>271.425</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M40" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N40" s="4" t="n">
-        <v>16311.65</v>
-      </c>
-      <c r="O40" s="8" t="n">
-        <v>6247.87</v>
+      <c r="N40" s="4">
+        <f>J40*E40</f>
+        <v/>
+      </c>
+      <c r="O40" s="8">
+        <f>N40-G40</f>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -3196,7 +3296,7 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
@@ -3204,11 +3304,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N41" s="4" t="n">
-        <v>64.33</v>
-      </c>
-      <c r="O41" s="8" t="n">
-        <v>0</v>
+      <c r="N41" s="4">
+        <f>H41</f>
+        <v/>
+      </c>
+      <c r="O41" s="8">
+        <f>N41-G41</f>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -3246,14 +3348,14 @@
         <v>1</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>683.16</v>
+        <v>672.1</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -3261,11 +3363,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N42" s="4" t="n">
-        <v>139225.28</v>
-      </c>
-      <c r="O42" s="8" t="n">
-        <v>80900.52</v>
+      <c r="N42" s="4">
+        <f>J42*E42</f>
+        <v/>
+      </c>
+      <c r="O42" s="8">
+        <f>N42-G42</f>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -3303,14 +3407,14 @@
         <v>1.24</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>263.7</v>
+        <v>258.33</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>36</v>
+        <v>0.58</v>
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -3318,11 +3422,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N43" s="4" t="n">
-        <v>124797.08</v>
-      </c>
-      <c r="O43" s="8" t="n">
-        <v>61783.24</v>
+      <c r="N43" s="4">
+        <f>J43*E43</f>
+        <v/>
+      </c>
+      <c r="O43" s="8">
+        <f>N43-G43</f>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -3360,14 +3466,14 @@
         <v>1.03</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>177.1</v>
+        <v>174.25</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>100</v>
+        <v>1.58</v>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -3375,11 +3481,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N44" s="4" t="n">
-        <v>121693.56</v>
-      </c>
-      <c r="O44" s="8" t="n">
-        <v>69311.61</v>
+      <c r="N44" s="4">
+        <f>J44*E44</f>
+        <v/>
+      </c>
+      <c r="O44" s="8">
+        <f>N44-G44</f>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -3417,14 +3525,14 @@
         <v>0.99</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>390.57</v>
+        <v>384.43</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>1.36</v>
+        <v>0.77</v>
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -3432,11 +3540,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N45" s="4" t="n">
-        <v>56782.24</v>
-      </c>
-      <c r="O45" s="8" t="n">
-        <v>25748.69</v>
+      <c r="N45" s="4">
+        <f>J45*E45</f>
+        <v/>
+      </c>
+      <c r="O45" s="8">
+        <f>N45-G45</f>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -3474,14 +3584,14 @@
         <v>1.22</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>126.48</v>
+        <v>123.6</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -3489,11 +3599,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N46" s="4" t="n">
-        <v>42509.3</v>
-      </c>
-      <c r="O46" s="8" t="n">
-        <v>16316.35</v>
+      <c r="N46" s="4">
+        <f>J46*E46</f>
+        <v/>
+      </c>
+      <c r="O46" s="8">
+        <f>N46-G46</f>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -3538,7 +3650,7 @@
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
@@ -3546,11 +3658,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N47" s="4" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="O47" s="8" t="n">
-        <v>0</v>
+      <c r="N47" s="4">
+        <f>H47</f>
+        <v/>
+      </c>
+      <c r="O47" s="8">
+        <f>N47-G47</f>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -3595,7 +3709,7 @@
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M48" s="11" t="inlineStr">
@@ -3603,11 +3717,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N48" s="4" t="n">
-        <v>200120.16</v>
-      </c>
-      <c r="O48" s="8" t="n">
-        <v>0</v>
+      <c r="N48" s="4">
+        <f>H48</f>
+        <v/>
+      </c>
+      <c r="O48" s="8">
+        <f>N48-G48</f>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -3652,7 +3768,7 @@
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
@@ -3660,11 +3776,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N49" s="4" t="n">
-        <v>100019.49</v>
-      </c>
-      <c r="O49" s="8" t="n">
-        <v>0</v>
+      <c r="N49" s="4">
+        <f>H49</f>
+        <v/>
+      </c>
+      <c r="O49" s="8">
+        <f>N49-G49</f>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -3709,7 +3827,7 @@
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M50" s="11" t="inlineStr">
@@ -3717,11 +3835,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N50" s="4" t="n">
-        <v>193000</v>
-      </c>
-      <c r="O50" s="8" t="n">
-        <v>0</v>
+      <c r="N50" s="4">
+        <f>H50</f>
+        <v/>
+      </c>
+      <c r="O50" s="8">
+        <f>N50-G50</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -3766,7 +3886,7 @@
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
@@ -3774,11 +3894,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N51" s="4" t="n">
-        <v>80000</v>
-      </c>
-      <c r="O51" s="8" t="n">
-        <v>0</v>
+      <c r="N51" s="4">
+        <f>H51</f>
+        <v/>
+      </c>
+      <c r="O51" s="8">
+        <f>N51-G51</f>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -3823,7 +3945,7 @@
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M52" s="11" t="inlineStr">
@@ -3831,11 +3953,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N52" s="4" t="n">
-        <v>22000</v>
-      </c>
-      <c r="O52" s="8" t="n">
-        <v>2000</v>
+      <c r="N52" s="4">
+        <f>H52</f>
+        <v/>
+      </c>
+      <c r="O52" s="8">
+        <f>N52-G52</f>
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -3880,7 +4004,7 @@
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
@@ -3888,11 +4012,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N53" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="O53" s="8" t="n">
-        <v>0</v>
+      <c r="N53" s="4">
+        <f>H53</f>
+        <v/>
+      </c>
+      <c r="O53" s="8">
+        <f>N53-G53</f>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -3937,7 +4063,7 @@
       </c>
       <c r="L54" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -3945,11 +4071,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N54" s="4" t="n">
-        <v>56711.87</v>
-      </c>
-      <c r="O54" s="8" t="n">
-        <v>0</v>
+      <c r="N54" s="4">
+        <f>H54</f>
+        <v/>
+      </c>
+      <c r="O54" s="8">
+        <f>N54-G54</f>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -3994,7 +4122,7 @@
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -4002,11 +4130,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N55" s="4" t="n">
-        <v>19485.83</v>
-      </c>
-      <c r="O55" s="8" t="n">
-        <v>0</v>
+      <c r="N55" s="4">
+        <f>H55</f>
+        <v/>
+      </c>
+      <c r="O55" s="8">
+        <f>N55-G55</f>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -4051,7 +4181,7 @@
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -4059,11 +4189,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N56" s="4" t="n">
-        <v>9943.360000000001</v>
-      </c>
-      <c r="O56" s="8" t="n">
-        <v>0</v>
+      <c r="N56" s="4">
+        <f>H56</f>
+        <v/>
+      </c>
+      <c r="O56" s="8">
+        <f>N56-G56</f>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -4108,7 +4240,7 @@
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -4116,11 +4248,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N57" s="4" t="n">
-        <v>8048.2</v>
-      </c>
-      <c r="O57" s="8" t="n">
-        <v>0</v>
+      <c r="N57" s="4">
+        <f>H57</f>
+        <v/>
+      </c>
+      <c r="O57" s="8">
+        <f>N57-G57</f>
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -4165,7 +4299,7 @@
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M58" s="11" t="inlineStr">
@@ -4173,11 +4307,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N58" s="4" t="n">
-        <v>70333</v>
-      </c>
-      <c r="O58" s="8" t="n">
-        <v>0</v>
+      <c r="N58" s="4">
+        <f>H58</f>
+        <v/>
+      </c>
+      <c r="O58" s="8">
+        <f>N58-G58</f>
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -4222,19 +4358,21 @@
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M59" s="14" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M59" s="13" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
       </c>
-      <c r="N59" s="4" t="n">
-        <v>16564</v>
-      </c>
-      <c r="O59" s="10" t="n">
-        <v>-1436</v>
+      <c r="N59" s="4">
+        <f>H59</f>
+        <v/>
+      </c>
+      <c r="O59" s="8">
+        <f>N59-G59</f>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -4279,7 +4417,7 @@
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M60" s="11" t="inlineStr">
@@ -4287,11 +4425,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N60" s="4" t="n">
-        <v>80891.74000000001</v>
-      </c>
-      <c r="O60" s="8" t="n">
-        <v>0</v>
+      <c r="N60" s="4">
+        <f>H60</f>
+        <v/>
+      </c>
+      <c r="O60" s="8">
+        <f>N60-G60</f>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -4336,7 +4476,7 @@
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
@@ -4344,11 +4484,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N61" s="4" t="n">
-        <v>70343.49000000001</v>
-      </c>
-      <c r="O61" s="8" t="n">
-        <v>0</v>
+      <c r="N61" s="4">
+        <f>H61</f>
+        <v/>
+      </c>
+      <c r="O61" s="8">
+        <f>N61-G61</f>
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -4386,14 +4528,14 @@
         <v>1</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>683.16</v>
+        <v>672.1</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -4401,11 +4543,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n">
-        <v>782.22</v>
-      </c>
-      <c r="O62" s="8" t="n">
-        <v>28.9</v>
+      <c r="N62" s="4">
+        <f>J62*E62</f>
+        <v/>
+      </c>
+      <c r="O62" s="8">
+        <f>N62-G62</f>
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -4443,26 +4587,28 @@
         <v>0.77</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>59.08</v>
+        <v>58.515</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>10.11</v>
+        <v>0</v>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M63" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M63" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N63" s="4" t="n">
-        <v>55.18</v>
-      </c>
-      <c r="O63" s="8" t="n">
-        <v>0.39</v>
+      <c r="N63" s="4">
+        <f>J63*E63</f>
+        <v/>
+      </c>
+      <c r="O63" s="8">
+        <f>N63-G63</f>
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -4507,7 +4653,7 @@
       </c>
       <c r="L64" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M64" s="11" t="inlineStr">
@@ -4515,11 +4661,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N64" s="4" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="O64" s="8" t="n">
-        <v>0</v>
+      <c r="N64" s="4">
+        <f>H64</f>
+        <v/>
+      </c>
+      <c r="O64" s="8">
+        <f>N64-G64</f>
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -4564,7 +4712,7 @@
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
@@ -4572,11 +4720,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N65" s="4" t="n">
-        <v>68549.10000000001</v>
-      </c>
-      <c r="O65" s="8" t="n">
-        <v>0</v>
+      <c r="N65" s="4">
+        <f>H65</f>
+        <v/>
+      </c>
+      <c r="O65" s="8">
+        <f>N65-G65</f>
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -4614,26 +4764,28 @@
         <v>0.572</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>75.01000000000001</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>95</v>
+        <v>0.97</v>
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M66" s="13" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M66" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="N66" s="4" t="n">
-        <v>10810.22</v>
-      </c>
-      <c r="O66" s="10" t="n">
-        <v>-886.28</v>
+      <c r="N66" s="4">
+        <f>J66*E66</f>
+        <v/>
+      </c>
+      <c r="O66" s="8">
+        <f>N66-G66</f>
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -4671,26 +4823,28 @@
         <v>1.076</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>47.06</v>
+        <v>45.475</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>1.7</v>
+        <v>2.71</v>
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M67" s="13" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M67" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="N67" s="4" t="n">
-        <v>10917.92</v>
-      </c>
-      <c r="O67" s="8" t="n">
-        <v>71.92</v>
+      <c r="N67" s="4">
+        <f>J67*E67</f>
+        <v/>
+      </c>
+      <c r="O67" s="8">
+        <f>N67-G67</f>
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -4735,7 +4889,7 @@
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M68" s="11" t="inlineStr">
@@ -4743,11 +4897,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N68" s="4" t="n">
-        <v>360.56</v>
-      </c>
-      <c r="O68" s="8" t="n">
-        <v>0</v>
+      <c r="N68" s="4">
+        <f>H68</f>
+        <v/>
+      </c>
+      <c r="O68" s="8">
+        <f>N68-G68</f>
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -4785,24 +4941,28 @@
         <v>0.617</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>487.77</v>
-      </c>
-      <c r="K69" s="12" t="n"/>
+        <v>482.43</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M69" s="13" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M69" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="N69" s="4" t="n">
-        <v>11286.51</v>
-      </c>
-      <c r="O69" s="8" t="n">
-        <v>308.8</v>
+      <c r="N69" s="4">
+        <f>J69*E69</f>
+        <v/>
+      </c>
+      <c r="O69" s="8">
+        <f>N69-G69</f>
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -4840,26 +5000,28 @@
         <v>2.202</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>208.19</v>
+        <v>201.43</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>48</v>
+        <v>0.02</v>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M70" s="13" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M70" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="N70" s="4" t="n">
-        <v>2230.34</v>
-      </c>
-      <c r="O70" s="8" t="n">
-        <v>70.09</v>
+      <c r="N70" s="4">
+        <f>J70*E70</f>
+        <v/>
+      </c>
+      <c r="O70" s="8">
+        <f>N70-G70</f>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -4897,26 +5059,28 @@
         <v>0.405</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>33.22</v>
+        <v>34.8</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>4.09</v>
+        <v>5.11</v>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M71" s="13" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M71" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="N71" s="4" t="n">
-        <v>1764.31</v>
-      </c>
-      <c r="O71" s="10" t="n">
-        <v>-126.16</v>
+      <c r="N71" s="4">
+        <f>J71*E71</f>
+        <v/>
+      </c>
+      <c r="O71" s="8">
+        <f>N71-G71</f>
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -4961,7 +5125,7 @@
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M72" s="11" t="inlineStr">
@@ -4969,11 +5133,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N72" s="4" t="n">
-        <v>423.89</v>
-      </c>
-      <c r="O72" s="8" t="n">
-        <v>0</v>
+      <c r="N72" s="4">
+        <f>H72</f>
+        <v/>
+      </c>
+      <c r="O72" s="8">
+        <f>N72-G72</f>
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -5011,24 +5177,28 @@
         <v>2.552</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>68.29000000000001</v>
-      </c>
-      <c r="K73" s="12" t="n"/>
+        <v>67.11020000000001</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M73" s="13" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M73" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="N73" s="4" t="n">
-        <v>136.58</v>
-      </c>
-      <c r="O73" s="10" t="n">
-        <v>-5.94</v>
+      <c r="N73" s="4">
+        <f>J73*E73</f>
+        <v/>
+      </c>
+      <c r="O73" s="8">
+        <f>N73-G73</f>
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -5066,24 +5236,28 @@
         <v>0.678</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>29.23</v>
-      </c>
-      <c r="K74" s="12" t="n"/>
+        <v>27.54</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M74" s="13" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M74" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="N74" s="4" t="n">
-        <v>29.23</v>
-      </c>
-      <c r="O74" s="10" t="n">
-        <v>-5.97</v>
+      <c r="N74" s="4">
+        <f>J74*E74</f>
+        <v/>
+      </c>
+      <c r="O74" s="8">
+        <f>N74-G74</f>
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -5128,7 +5302,7 @@
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -5136,11 +5310,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N75" s="4" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="O75" s="8" t="n">
-        <v>0</v>
+      <c r="N75" s="4">
+        <f>H75</f>
+        <v/>
+      </c>
+      <c r="O75" s="8">
+        <f>N75-G75</f>
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -5185,7 +5361,7 @@
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M76" s="11" t="inlineStr">
@@ -5193,11 +5369,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N76" s="4" t="n">
-        <v>10883.52</v>
-      </c>
-      <c r="O76" s="8" t="n">
-        <v>5069.84</v>
+      <c r="N76" s="4">
+        <f>H76</f>
+        <v/>
+      </c>
+      <c r="O76" s="8">
+        <f>N76-G76</f>
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -5242,7 +5420,7 @@
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
@@ -5250,11 +5428,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N77" s="4" t="n">
-        <v>4007.12</v>
-      </c>
-      <c r="O77" s="8" t="n">
-        <v>0</v>
+      <c r="N77" s="4">
+        <f>H77</f>
+        <v/>
+      </c>
+      <c r="O77" s="8">
+        <f>N77-G77</f>
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -5299,7 +5479,7 @@
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M78" s="11" t="inlineStr">
@@ -5307,11 +5487,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N78" s="4" t="n">
-        <v>1000.09</v>
-      </c>
-      <c r="O78" s="8" t="n">
-        <v>0</v>
+      <c r="N78" s="4">
+        <f>H78</f>
+        <v/>
+      </c>
+      <c r="O78" s="8">
+        <f>N78-G78</f>
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -5356,7 +5538,7 @@
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
@@ -5364,11 +5546,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N79" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O79" s="8" t="n">
-        <v>0</v>
+      <c r="N79" s="4">
+        <f>H79</f>
+        <v/>
+      </c>
+      <c r="O79" s="8">
+        <f>N79-G79</f>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -5413,7 +5597,7 @@
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M80" s="7" t="inlineStr">
@@ -5421,11 +5605,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N80" s="4" t="n">
-        <v>392.29</v>
-      </c>
-      <c r="O80" s="8" t="n">
-        <v>0</v>
+      <c r="N80" s="4">
+        <f>H80</f>
+        <v/>
+      </c>
+      <c r="O80" s="8">
+        <f>N80-G80</f>
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -5470,7 +5656,7 @@
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
@@ -5478,11 +5664,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N81" s="4" t="n">
-        <v>370.54</v>
-      </c>
-      <c r="O81" s="8" t="n">
-        <v>0</v>
+      <c r="N81" s="4">
+        <f>H81</f>
+        <v/>
+      </c>
+      <c r="O81" s="8">
+        <f>N81-G81</f>
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -5527,7 +5715,7 @@
       </c>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
@@ -5535,11 +5723,13 @@
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="N82" s="4" t="n">
-        <v>157.36</v>
-      </c>
-      <c r="O82" s="8" t="n">
-        <v>0</v>
+      <c r="N82" s="4">
+        <f>H82</f>
+        <v/>
+      </c>
+      <c r="O82" s="8">
+        <f>N82-G82</f>
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -5577,26 +5767,26 @@
         <v>3.91</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>73.72</v>
-      </c>
-      <c r="K83" s="5" t="n">
-        <v>37</v>
-      </c>
+        <v>71.67</v>
+      </c>
+      <c r="K83" s="9" t="n"/>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M83" s="9" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M83" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
         </is>
       </c>
-      <c r="N83" s="4" t="n">
-        <v>589.76</v>
-      </c>
-      <c r="O83" s="8" t="n">
-        <v>386.03</v>
+      <c r="N83" s="4">
+        <f>J83*E83</f>
+        <v/>
+      </c>
+      <c r="O83" s="8">
+        <f>N83-G83</f>
+        <v/>
       </c>
     </row>
     <row r="84">
@@ -5641,7 +5831,7 @@
       </c>
       <c r="L84" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M84" s="11" t="inlineStr">
@@ -5649,11 +5839,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N84" s="4" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="O84" s="8" t="n">
-        <v>0</v>
+      <c r="N84" s="4">
+        <f>H84</f>
+        <v/>
+      </c>
+      <c r="O84" s="8">
+        <f>N84-G84</f>
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -5698,19 +5890,21 @@
       </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
-        </is>
-      </c>
-      <c r="M85" s="14" t="inlineStr">
+          <t>2026-06-11 11:43:19</t>
+        </is>
+      </c>
+      <c r="M85" s="13" t="inlineStr">
         <is>
           <t>Crypto</t>
         </is>
       </c>
-      <c r="N85" s="4" t="n">
-        <v>28.71</v>
-      </c>
-      <c r="O85" s="8" t="n">
-        <v>0</v>
+      <c r="N85" s="4">
+        <f>H85</f>
+        <v/>
+      </c>
+      <c r="O85" s="8">
+        <f>N85-G85</f>
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -5755,7 +5949,7 @@
       </c>
       <c r="L86" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M86" s="11" t="inlineStr">
@@ -5763,11 +5957,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O86" s="8" t="n">
-        <v>0</v>
+      <c r="N86" s="4">
+        <f>H86</f>
+        <v/>
+      </c>
+      <c r="O86" s="8">
+        <f>N86-G86</f>
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -5812,7 +6008,7 @@
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
@@ -5820,11 +6016,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N87" s="4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O87" s="8" t="n">
-        <v>0</v>
+      <c r="N87" s="4">
+        <f>H87</f>
+        <v/>
+      </c>
+      <c r="O87" s="8">
+        <f>N87-G87</f>
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -5869,7 +6067,7 @@
       </c>
       <c r="L88" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09 21:06:35</t>
+          <t>2026-06-11 11:43:19</t>
         </is>
       </c>
       <c r="M88" s="11" t="inlineStr">
@@ -5877,11 +6075,13 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="N88" s="4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O88" s="8" t="n">
-        <v>0</v>
+      <c r="N88" s="4">
+        <f>H88</f>
+        <v/>
+      </c>
+      <c r="O88" s="8">
+        <f>N88-G88</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/output.xlsx
+++ b/output.xlsx
@@ -675,7 +675,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-11 11:43:19</t>
+          <t>Generated: 2026-06-11 12:37:49</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B6" s="18" t="n">
-        <v>5979586.3030085</v>
+        <v>5981591.562387399</v>
       </c>
       <c r="C6" s="18" t="n">
         <v>3949239.310000001</v>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B7" s="20" t="n">
-        <v>266685.4630085006</v>
+        <v>268690.7223873995</v>
       </c>
       <c r="C7" s="19" t="n"/>
       <c r="D7" s="19" t="n"/>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>4.668126937216377</v>
+        <v>4.703227483069696</v>
       </c>
       <c r="C8" s="19" t="n"/>
       <c r="D8" s="19" t="n"/>
@@ -779,10 +779,10 @@
         </is>
       </c>
       <c r="B11" s="23" t="n">
-        <v>266284.40597</v>
+        <v>267088.0751464</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>4.453224562308344</v>
+        <v>4.465167378292185</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="B12" s="26" t="n">
-        <v>1248510.0912685</v>
+        <v>1249711.681471</v>
       </c>
       <c r="C12" s="27" t="n">
-        <v>20.87953962033024</v>
+        <v>20.8926281314368</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -808,7 +808,7 @@
         <v>3166486.21577</v>
       </c>
       <c r="C13" s="30" t="n">
-        <v>52.95493793904858</v>
+        <v>52.93718540866368</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -821,7 +821,7 @@
         <v>1281712.88</v>
       </c>
       <c r="C14" s="33" t="n">
-        <v>21.43480861468851</v>
+        <v>21.42762284304877</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -834,7 +834,7 @@
         <v>16592.71</v>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0.2774892636243369</v>
+        <v>0.2773962385585793</v>
       </c>
     </row>
     <row r="16">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="B16" s="37" t="n">
-        <v>5979586.3030085</v>
+        <v>5981591.562387399</v>
       </c>
       <c r="C16" s="38" t="n">
         <v>100</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -1108,12 +1108,12 @@
         <v>1.42</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>113.65</v>
+        <v>113.92</v>
       </c>
       <c r="K4" s="9" t="n"/>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -1342,14 +1342,14 @@
         <v>0.62</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>286.55</v>
+        <v>286.31</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1460,14 +1460,14 @@
         <v>1.23</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>85.33</v>
+        <v>85.56</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
@@ -1519,14 +1519,14 @@
         <v>0.7</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>158.15</v>
+        <v>158.16</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>2.21</v>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
@@ -1578,14 +1578,14 @@
         <v>0.59</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>32.495</v>
+        <v>32.4738</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
@@ -1637,14 +1637,14 @@
         <v>1.798</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>386.08</v>
+        <v>387.265</v>
       </c>
       <c r="K13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
@@ -1696,14 +1696,14 @@
         <v>1.086</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>293.045</v>
+        <v>294.49</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>0.36</v>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M14" s="12" t="inlineStr">
@@ -1755,14 +1755,14 @@
         <v>1.25</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>383.93</v>
+        <v>383.9791</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
@@ -1814,14 +1814,14 @@
         <v>1</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>670.1</v>
+        <v>671.0281</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>0.82</v>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -1932,14 +1932,14 @@
         <v>1</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>670.1</v>
+        <v>671.0281</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0.82</v>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -2050,14 +2050,14 @@
         <v>0.92</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>83.60850000000001</v>
+        <v>83.625</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>2.66</v>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
@@ -2109,14 +2109,14 @@
         <v>0.98</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>153.14</v>
+        <v>153.24</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
@@ -2286,14 +2286,14 @@
         <v>0.7</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>158.15</v>
+        <v>158.16</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>2.21</v>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
@@ -2345,14 +2345,14 @@
         <v>0.59</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>32.495</v>
+        <v>32.4738</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -2758,14 +2758,14 @@
         <v>0.92</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>83.60850000000001</v>
+        <v>83.625</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>2.66</v>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr">
@@ -2817,14 +2817,14 @@
         <v>1.798</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>386.08</v>
+        <v>387.265</v>
       </c>
       <c r="K33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
@@ -2876,14 +2876,14 @@
         <v>2.202</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>201.43</v>
+        <v>201.9042</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>0.02</v>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M34" s="12" t="inlineStr">
@@ -2935,14 +2935,14 @@
         <v>0.59</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>32.495</v>
+        <v>32.4738</v>
       </c>
       <c r="K35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -3053,14 +3053,14 @@
         <v>1.086</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>293.045</v>
+        <v>294.49</v>
       </c>
       <c r="K37" s="5" t="n">
         <v>0.36</v>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M37" s="12" t="inlineStr">
@@ -3112,14 +3112,14 @@
         <v>1.97</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>589.5599999999999</v>
+        <v>591.295</v>
       </c>
       <c r="K38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M38" s="10" t="inlineStr">
@@ -3171,14 +3171,14 @@
         <v>1.64</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>154.65</v>
+        <v>154.84</v>
       </c>
       <c r="K39" s="5" t="n">
         <v>0.73</v>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M39" s="10" t="inlineStr">
@@ -3230,14 +3230,14 @@
         <v>1.41</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>271.425</v>
+        <v>271.82</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M40" s="10" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M48" s="11" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M50" s="11" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M52" s="11" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="L54" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M58" s="11" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M59" s="13" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M60" s="11" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -4587,14 +4587,14 @@
         <v>0.77</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>58.515</v>
+        <v>58.6586</v>
       </c>
       <c r="K63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M63" s="10" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="L64" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M64" s="11" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
@@ -4764,14 +4764,14 @@
         <v>0.572</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>74.79000000000001</v>
+        <v>74.95</v>
       </c>
       <c r="K66" s="5" t="n">
         <v>0.97</v>
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M66" s="12" t="inlineStr">
@@ -4823,14 +4823,14 @@
         <v>1.076</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>45.475</v>
+        <v>45.41</v>
       </c>
       <c r="K67" s="5" t="n">
         <v>2.71</v>
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M68" s="11" t="inlineStr">
@@ -4941,14 +4941,14 @@
         <v>0.617</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>482.43</v>
+        <v>482.16</v>
       </c>
       <c r="K69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
@@ -5000,14 +5000,14 @@
         <v>2.202</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>201.43</v>
+        <v>201.9042</v>
       </c>
       <c r="K70" s="5" t="n">
         <v>0.02</v>
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M70" s="12" t="inlineStr">
@@ -5059,14 +5059,14 @@
         <v>0.405</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>34.8</v>
+        <v>34.935</v>
       </c>
       <c r="K71" s="5" t="n">
         <v>5.11</v>
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M71" s="12" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M72" s="11" t="inlineStr">
@@ -5177,14 +5177,14 @@
         <v>2.552</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>67.11020000000001</v>
+        <v>67.41</v>
       </c>
       <c r="K73" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
@@ -5236,14 +5236,14 @@
         <v>0.678</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>27.54</v>
+        <v>28.16</v>
       </c>
       <c r="K74" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M74" s="12" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M76" s="11" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M78" s="11" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M80" s="7" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
@@ -5767,12 +5767,12 @@
         <v>3.91</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>71.67</v>
+        <v>72.325</v>
       </c>
       <c r="K83" s="9" t="n"/>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="L84" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M84" s="11" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M85" s="13" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="L86" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M86" s="11" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="L88" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:43:19</t>
+          <t>2026-06-11 12:37:49</t>
         </is>
       </c>
       <c r="M88" s="11" t="inlineStr">
